--- a/sheets/대금율보/검수/사랑의 기도.xlsx
+++ b/sheets/대금율보/검수/사랑의 기도.xlsx
@@ -3045,7 +3045,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋‹
+          <t xml:space="preserve">淋
 –湳</t>
         </is>
       </c>
@@ -3159,7 +3159,7 @@
       <c r="E9" s="25"/>
       <c r="F9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰‹
+          <t xml:space="preserve">汰
 –潢</t>
         </is>
       </c>
@@ -3188,7 +3188,7 @@
       <c r="E10" s="26"/>
       <c r="F10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">無‹
+          <t xml:space="preserve">無
 –南</t>
         </is>
       </c>
@@ -3299,7 +3299,7 @@
       <c r="G13" s="25"/>
       <c r="H13" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕‹
+          <t xml:space="preserve">潕
 –湳</t>
         </is>
       </c>
@@ -3343,7 +3343,7 @@
       <c r="G14" s="26"/>
       <c r="H14" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 淋汰</t>
         </is>
       </c>
@@ -3367,7 +3367,7 @@
       </c>
       <c r="D15" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳‹
+          <t xml:space="preserve">湳
 –湳</t>
         </is>
       </c>
@@ -3412,7 +3412,7 @@
       </c>
       <c r="D16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 湳
 洟</t>
         </is>
@@ -3440,7 +3440,7 @@
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢‹
+          <t xml:space="preserve">潢
 –潕</t>
         </is>
       </c>
@@ -3461,7 +3461,7 @@
       </c>
       <c r="F17" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">潕‹
+          <t xml:space="preserve">潕
 –潕</t>
         </is>
       </c>
@@ -3470,11 +3470,7 @@
           <t xml:space="preserve">마음</t>
         </is>
       </c>
-      <c r="H17" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H17" s="21"/>
       <c r="I17" s="25"/>
     </row>
     <row r="18" ht="56" customHeight="1">
@@ -3493,7 +3489,7 @@
       </c>
       <c r="D18" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 潕
 潢</t>
         </is>
@@ -3577,7 +3573,7 @@
       <c r="C20" s="25"/>
       <c r="D20" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">–‹
+          <t xml:space="preserve">–
 –汰</t>
         </is>
       </c>
@@ -3607,11 +3603,7 @@
       </c>
       <c r="F21" s="21"/>
       <c r="G21" s="25"/>
-      <c r="H21" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">‹</t>
-        </is>
-      </c>
+      <c r="H21" s="21"/>
       <c r="I21" s="25"/>
     </row>
     <row r="22" ht="56" customHeight="1">

--- a/sheets/대금율보/검수/사랑의 기도.xlsx
+++ b/sheets/대금율보/검수/사랑의 기도.xlsx
@@ -2923,20 +2923,20 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="102.56" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
       <c r="H2" s="20"/>
       <c r="I2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="91.8" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2996,7 +2996,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="91.8" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="21"/>
       <c r="C4" s="25"/>
@@ -3016,7 +3016,7 @@
       <c r="H4" s="21"/>
       <c r="I4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="91.8" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3041,7 +3041,7 @@
       <c r="H5" s="21"/>
       <c r="I5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="91.8" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -3090,7 +3090,7 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="91.8" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -3135,7 +3135,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="91.8" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21"/>
       <c r="C8" s="25"/>
@@ -3146,7 +3146,7 @@
       <c r="H8" s="21"/>
       <c r="I8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="91.8" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3171,7 +3171,7 @@
       <c r="H9" s="21"/>
       <c r="I9" s="25"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="91.8" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21" t="inlineStr">
         <is>
@@ -3209,7 +3209,7 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="91.8" customHeight="true">
       <c r="A11" s="0"/>
       <c r="B11" s="21" t="inlineStr">
         <is>
@@ -3252,7 +3252,7 @@
         </is>
       </c>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="91.8" customHeight="true">
       <c r="A12" s="0"/>
       <c r="B12" s="21"/>
       <c r="C12" s="25"/>
@@ -3281,7 +3281,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="91.8" customHeight="true">
       <c r="A13" s="0"/>
       <c r="B13" s="21"/>
       <c r="C13" s="25"/>
@@ -3309,7 +3309,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="91.8" customHeight="true">
       <c r="A14" s="0"/>
       <c r="B14" s="21" t="inlineStr">
         <is>
@@ -3353,7 +3353,7 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="91.8" customHeight="true">
       <c r="A15" s="0"/>
       <c r="B15" s="21" t="inlineStr">
         <is>
@@ -3397,7 +3397,7 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="91.8" customHeight="true">
       <c r="A16" s="0"/>
       <c r="B16" s="21" t="inlineStr">
         <is>
@@ -3436,7 +3436,7 @@
       <c r="H16" s="21"/>
       <c r="I16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="91.8" customHeight="true">
       <c r="A17" s="0"/>
       <c r="B17" s="21" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       <c r="H17" s="21"/>
       <c r="I17" s="25"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="91.8" customHeight="true">
       <c r="A18" s="0"/>
       <c r="B18" s="21" t="inlineStr">
         <is>
@@ -3524,7 +3524,7 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="56" customHeight="1">
+    <row r="19" ht="91.8" customHeight="true">
       <c r="A19" s="0"/>
       <c r="B19" s="21" t="inlineStr">
         <is>
@@ -3567,7 +3567,7 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="56" customHeight="1">
+    <row r="20" ht="91.8" customHeight="true">
       <c r="A20" s="0"/>
       <c r="B20" s="21"/>
       <c r="C20" s="25"/>
@@ -3587,7 +3587,7 @@
       <c r="H20" s="21"/>
       <c r="I20" s="25"/>
     </row>
-    <row r="21" ht="56" customHeight="1">
+    <row r="21" ht="91.8" customHeight="true">
       <c r="A21" s="0"/>
       <c r="B21" s="21"/>
       <c r="C21" s="25"/>
@@ -3606,7 +3606,7 @@
       <c r="H21" s="21"/>
       <c r="I21" s="25"/>
     </row>
-    <row r="22" ht="56" customHeight="1">
+    <row r="22" ht="91.8" customHeight="true">
       <c r="A22" s="0"/>
       <c r="B22" s="21" t="inlineStr">
         <is>
@@ -3653,6 +3653,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="62"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="39"/>
 </worksheet>
 </file>